--- a/CPMT_template.xlsx
+++ b/CPMT_template.xlsx
@@ -8,24 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seche\Documents\Benoit\Handball\TeamPointMonitoringTool\CTPM\static\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D20ECCF0-22AF-4943-8B23-1FFF3C4E7822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD715D4D-EE9F-42BD-8886-A2F91B9B952E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25950" yWindow="4590" windowWidth="21600" windowHeight="11295" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team (1)" sheetId="51" r:id="rId1"/>
-    <sheet name="Team (2)" sheetId="52" r:id="rId2"/>
-    <sheet name="Team (3)" sheetId="53" r:id="rId3"/>
-    <sheet name="Team (4)" sheetId="54" r:id="rId4"/>
-    <sheet name="Team (5)" sheetId="55" r:id="rId5"/>
-    <sheet name="Team (6)" sheetId="56" r:id="rId6"/>
-    <sheet name="Team (7)" sheetId="57" r:id="rId7"/>
-    <sheet name="Team (8)" sheetId="58" r:id="rId8"/>
-    <sheet name="Team (9)" sheetId="59" r:id="rId9"/>
-    <sheet name="Team (10)" sheetId="60" r:id="rId10"/>
-    <sheet name="Team (11)" sheetId="61" r:id="rId11"/>
-    <sheet name="Team (12)" sheetId="62" r:id="rId12"/>
-    <sheet name="Dropdownlist" sheetId="29" state="hidden" r:id="rId13"/>
+    <sheet name="Team (2)" sheetId="63" r:id="rId2"/>
+    <sheet name="Team (3)" sheetId="64" r:id="rId3"/>
+    <sheet name="Team (4)" sheetId="65" r:id="rId4"/>
+    <sheet name="Team (5)" sheetId="66" r:id="rId5"/>
+    <sheet name="Team (6)" sheetId="67" r:id="rId6"/>
+    <sheet name="Team (7)" sheetId="68" r:id="rId7"/>
+    <sheet name="Team (8)" sheetId="69" r:id="rId8"/>
+    <sheet name="Team (9)" sheetId="70" r:id="rId9"/>
+    <sheet name="Team (10)" sheetId="71" r:id="rId10"/>
+    <sheet name="Dropdownlist" sheetId="29" state="hidden" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +43,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="824" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="691" uniqueCount="52">
   <si>
     <t>1.0</t>
   </si>
@@ -198,6 +196,9 @@
   </si>
   <si>
     <t>Gender_Genre</t>
+  </si>
+  <si>
+    <t>N</t>
   </si>
 </sst>
 </file>
@@ -656,7 +657,316 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0268AB31-72C1-4DA9-BA08-F1E814EDFC60}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
@@ -732,6 +1042,2478 @@
               <a:srgbClr val="FF0000"/>
             </a:solidFill>
           </a:endParaRPr>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DCA8A5C4-380E-4363-8429-9840C9E76EB3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{73CA734B-D089-43F4-AF2F-4C57822B6C62}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1C5E57A0-402A-4691-A339-762CEFC69E5F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F83CFCD6-536C-4430-8417-503327FCC459}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{DAAB892C-FBF4-4A72-A992-EDABAE9F644A}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{07E1E071-97DA-4824-A7AA-913A47B828F0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing8.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6F81FA92-D1B6-410B-89E0-D41093E9E463}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing9.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>107948</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>41274</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Rectangle: Rounded Corners 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CDD94E1F-1071-41F8-92DD-C20C4CB133D7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7289798" y="41274"/>
+          <a:ext cx="3644902" cy="3101976"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst>
+            <a:gd name="adj" fmla="val 4902"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1">
+            <a:lumMod val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (FR)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" b="0" u="none">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t> </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Equipes</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Une équipe par onglet. Le nom de l'équipe peut etre modifié en changeant le nom de l'onglet. </a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Joueurs</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Compléter le tableau. Une ligne par joueur, chaque champ est obligatoire (à l'exception de la date de naissance).</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" baseline="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>--------------------------------------------</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000" baseline="0">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" b="1" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Instructions (EN)</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Teams</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: One team per tab. The team name can be updated by editing the tab name.</a:t>
+          </a:r>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:endParaRPr lang="en-US" sz="1000">
+            <a:solidFill>
+              <a:sysClr val="windowText" lastClr="000000"/>
+            </a:solidFill>
+            <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:pPr algn="l"/>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>+ </a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000" u="sng">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>Players</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" sz="1000">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:latin typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+              <a:cs typeface="Courier New" panose="02070309020205020404" pitchFamily="49" charset="0"/>
+            </a:rPr>
+            <a:t>: Fill-in the table. One line per player; all fields are required (except the date of birth).</a:t>
+          </a:r>
         </a:p>
       </xdr:txBody>
     </xdr:sp>
@@ -939,18 +3721,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CF96074F-7E3D-49B6-B84F-4E4CA7E75F70}">
   <dimension ref="A1:I50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" customWidth="1"/>
-    <col min="4" max="4" width="18.36328125" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -973,7 +3755,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -997,7 +3779,7 @@
       </c>
       <c r="I2" s="3"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1020,7 +3802,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1043,7 +3825,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1066,7 +3848,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1089,7 +3871,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1112,7 +3894,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1135,7 +3917,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1158,7 +3940,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1181,7 +3963,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1204,7 +3986,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1227,7 +4009,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1250,7 +4032,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1259,7 +4041,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1268,7 +4050,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1277,7 +4059,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1286,7 +4068,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1295,7 +4077,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1304,7 +4086,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1313,7 +4095,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1322,7 +4104,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -1331,7 +4113,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -1340,7 +4122,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -1349,7 +4131,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -1358,7 +4140,7 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
       <c r="C26" s="10"/>
@@ -1367,7 +4149,7 @@
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
       <c r="C27" s="10"/>
@@ -1376,7 +4158,7 @@
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -1385,7 +4167,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -1394,7 +4176,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -1403,7 +4185,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -1412,7 +4194,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -1421,7 +4203,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -1430,7 +4212,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -1439,7 +4221,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -1448,7 +4230,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -1457,7 +4239,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -1466,7 +4248,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -1475,7 +4257,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -1484,7 +4266,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -1493,7 +4275,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -1502,7 +4284,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -1511,7 +4293,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -1520,7 +4302,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -1529,7 +4311,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -1538,7 +4320,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -1547,7 +4329,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -1556,7 +4338,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -1565,7 +4347,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -1574,7 +4356,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -1589,12 +4371,12 @@
   <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{419AC268-099B-4BDD-8CC2-87FD61EA95FF}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7721780A-5227-4AAF-81F7-4979959C692B}">
           <x14:formula1>
@@ -1608,6 +4390,12 @@
           </x14:formula1>
           <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1F86A277-62FB-4C21-9F76-56BA1A450EDE}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
       </x14:dataValidations>
     </ext>
   </extLst>
@@ -1615,20 +4403,20 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AF945FD-EDB9-4C87-990A-192E26B89C76}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6182740-D76C-4A22-898D-C1D13B89CA55}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -1651,7 +4439,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -1673,8 +4461,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -1697,7 +4486,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -1720,7 +4509,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -1743,7 +4532,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -1766,7 +4555,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -1789,7 +4578,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -1812,7 +4601,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -1835,7 +4624,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -1858,7 +4647,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -1881,7 +4670,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -1904,7 +4693,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -1927,7 +4716,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -1936,7 +4725,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -1945,7 +4734,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -1954,7 +4743,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -1963,7 +4752,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -1972,7 +4761,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -1981,7 +4770,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -1990,7 +4779,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -1999,7 +4788,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -2008,7 +4797,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -2017,7 +4806,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -2026,7 +4815,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -2035,25 +4824,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -2062,7 +4851,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -2071,7 +4860,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -2080,7 +4869,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -2089,7 +4878,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -2098,7 +4887,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -2107,7 +4896,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -2116,7 +4905,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -2125,7 +4914,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -2134,7 +4923,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -2143,7 +4932,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -2152,7 +4941,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -2161,7 +4950,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -2170,7 +4959,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -2179,7 +4968,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -2188,7 +4977,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -2197,7 +4986,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -2206,7 +4995,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -2215,7 +5004,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -2224,7 +5013,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -2233,7 +5022,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -2242,7 +5031,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -2251,7 +5040,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -2263,26 +5052,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{44C7CE4A-5816-4C2F-AC14-4730D6A45CB8}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{352505ED-C0B5-45C5-AC3A-EAF3CC07CE9F}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A1B49B89-AA15-4B19-87B2-1DAF602D109C}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{845E40E7-0AF9-4D53-B610-E02076BA1978}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{528C47A7-D5A2-429B-85F4-AC9D119ABDC5}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{54A055CC-D9BE-4C92-98ED-B9B1FAB841CC}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{22789640-5C27-42F4-BE4A-7C80F6C1070B}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2291,1367 +5087,14 @@
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{065EE7AD-E160-4AD8-B213-FA018AB2129F}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6">
-        <v>32143</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6">
-        <v>33028</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6">
-        <v>33915</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6">
-        <v>35842</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="6">
-        <v>36726</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="6">
-        <v>37612</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6">
-        <v>33383</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="6">
-        <v>34243</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="6">
-        <v>34762</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6">
-        <v>35649</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="6">
-        <v>33977</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="6">
-        <v>34861</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="9"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="9"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{171EDB17-035B-49A4-9B21-B2597C6A7A42}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{40C8B2F7-0934-4788-9B7D-53AE2AB2FD51}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{427C2CCF-8CA0-4C2C-9E19-EE2A8AD487A8}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67B67078-925C-49DA-B40E-6AA02444BDD0}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
-      <c r="A1" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="B1" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C1" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>49</v>
-      </c>
-      <c r="E1" s="11" t="s">
-        <v>50</v>
-      </c>
-      <c r="F1" s="11" t="s">
-        <v>35</v>
-      </c>
-      <c r="G1" s="12" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" s="6">
-        <v>32143</v>
-      </c>
-      <c r="E2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F2" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4">
-        <v>2</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6">
-        <v>33028</v>
-      </c>
-      <c r="E3" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F3" s="7" t="s">
-        <v>1</v>
-      </c>
-      <c r="G3" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="6">
-        <v>33915</v>
-      </c>
-      <c r="E4" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>26</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="D5" s="6">
-        <v>35842</v>
-      </c>
-      <c r="E5" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G5" s="5" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4">
-        <v>5</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="D6" s="6">
-        <v>36726</v>
-      </c>
-      <c r="E6" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F6" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="G6" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="6">
-        <v>37612</v>
-      </c>
-      <c r="E7" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4">
-        <v>7</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D8" s="6">
-        <v>33383</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G8" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4">
-        <v>8</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="D9" s="6">
-        <v>34243</v>
-      </c>
-      <c r="E9" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G9" s="5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4">
-        <v>9</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>18</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="D10" s="6">
-        <v>34762</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4">
-        <v>10</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" s="6">
-        <v>35649</v>
-      </c>
-      <c r="E11" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>11</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D12" s="6">
-        <v>33977</v>
-      </c>
-      <c r="E12" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="D13" s="6">
-        <v>34861</v>
-      </c>
-      <c r="E13" s="7" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>31</v>
-      </c>
-      <c r="G13" s="5" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-      <c r="B14" s="9"/>
-      <c r="C14" s="9"/>
-      <c r="D14" s="10"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-      <c r="B15" s="9"/>
-      <c r="C15" s="9"/>
-      <c r="D15" s="10"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-      <c r="B16" s="9"/>
-      <c r="C16" s="9"/>
-      <c r="D16" s="10"/>
-      <c r="E16" s="8"/>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-      <c r="B17" s="9"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="10"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-      <c r="B18" s="9"/>
-      <c r="C18" s="9"/>
-      <c r="D18" s="10"/>
-      <c r="E18" s="8"/>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-      <c r="B19" s="9"/>
-      <c r="C19" s="9"/>
-      <c r="D19" s="10"/>
-      <c r="E19" s="8"/>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-      <c r="B20" s="9"/>
-      <c r="C20" s="9"/>
-      <c r="D20" s="10"/>
-      <c r="E20" s="8"/>
-      <c r="F20" s="8"/>
-      <c r="G20" s="9"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-      <c r="B21" s="9"/>
-      <c r="C21" s="9"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="8"/>
-      <c r="F21" s="8"/>
-      <c r="G21" s="9"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-      <c r="B22" s="9"/>
-      <c r="C22" s="9"/>
-      <c r="D22" s="10"/>
-      <c r="E22" s="8"/>
-      <c r="F22" s="8"/>
-      <c r="G22" s="9"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-      <c r="B23" s="9"/>
-      <c r="C23" s="9"/>
-      <c r="D23" s="10"/>
-      <c r="E23" s="8"/>
-      <c r="F23" s="8"/>
-      <c r="G23" s="9"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-      <c r="B24" s="9"/>
-      <c r="C24" s="9"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="8"/>
-      <c r="F24" s="8"/>
-      <c r="G24" s="9"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-      <c r="B25" s="9"/>
-      <c r="C25" s="9"/>
-      <c r="D25" s="10"/>
-      <c r="E25" s="8"/>
-      <c r="F25" s="8"/>
-      <c r="G25" s="9"/>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-      <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
-      <c r="E26" s="8"/>
-      <c r="F26" s="8"/>
-      <c r="G26" s="9"/>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-      <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
-      <c r="E27" s="8"/>
-      <c r="F27" s="8"/>
-      <c r="G27" s="9"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-      <c r="B28" s="9"/>
-      <c r="C28" s="9"/>
-      <c r="D28" s="10"/>
-      <c r="E28" s="8"/>
-      <c r="F28" s="8"/>
-      <c r="G28" s="9"/>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-      <c r="B29" s="9"/>
-      <c r="C29" s="9"/>
-      <c r="D29" s="10"/>
-      <c r="E29" s="8"/>
-      <c r="F29" s="8"/>
-      <c r="G29" s="9"/>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-      <c r="B30" s="9"/>
-      <c r="C30" s="9"/>
-      <c r="D30" s="10"/>
-      <c r="E30" s="8"/>
-      <c r="F30" s="8"/>
-      <c r="G30" s="9"/>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-      <c r="B31" s="9"/>
-      <c r="C31" s="9"/>
-      <c r="D31" s="10"/>
-      <c r="E31" s="8"/>
-      <c r="F31" s="8"/>
-      <c r="G31" s="9"/>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-      <c r="B32" s="9"/>
-      <c r="C32" s="9"/>
-      <c r="D32" s="10"/>
-      <c r="E32" s="8"/>
-      <c r="F32" s="8"/>
-      <c r="G32" s="9"/>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-      <c r="B33" s="9"/>
-      <c r="C33" s="9"/>
-      <c r="D33" s="10"/>
-      <c r="E33" s="8"/>
-      <c r="F33" s="8"/>
-      <c r="G33" s="9"/>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-      <c r="B34" s="9"/>
-      <c r="C34" s="9"/>
-      <c r="D34" s="10"/>
-      <c r="E34" s="8"/>
-      <c r="F34" s="8"/>
-      <c r="G34" s="9"/>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-      <c r="B35" s="9"/>
-      <c r="C35" s="9"/>
-      <c r="D35" s="10"/>
-      <c r="E35" s="8"/>
-      <c r="F35" s="8"/>
-      <c r="G35" s="9"/>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-      <c r="B36" s="9"/>
-      <c r="C36" s="9"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="8"/>
-      <c r="F36" s="8"/>
-      <c r="G36" s="9"/>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-      <c r="B37" s="9"/>
-      <c r="C37" s="9"/>
-      <c r="D37" s="10"/>
-      <c r="E37" s="8"/>
-      <c r="F37" s="8"/>
-      <c r="G37" s="9"/>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-      <c r="B38" s="9"/>
-      <c r="C38" s="9"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="8"/>
-      <c r="F38" s="8"/>
-      <c r="G38" s="9"/>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-      <c r="B39" s="9"/>
-      <c r="C39" s="9"/>
-      <c r="D39" s="10"/>
-      <c r="E39" s="8"/>
-      <c r="F39" s="8"/>
-      <c r="G39" s="9"/>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-      <c r="B40" s="9"/>
-      <c r="C40" s="9"/>
-      <c r="D40" s="10"/>
-      <c r="E40" s="8"/>
-      <c r="F40" s="8"/>
-      <c r="G40" s="9"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-      <c r="B41" s="9"/>
-      <c r="C41" s="9"/>
-      <c r="D41" s="10"/>
-      <c r="E41" s="8"/>
-      <c r="F41" s="8"/>
-      <c r="G41" s="9"/>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-      <c r="B42" s="9"/>
-      <c r="C42" s="9"/>
-      <c r="D42" s="10"/>
-      <c r="E42" s="8"/>
-      <c r="F42" s="8"/>
-      <c r="G42" s="9"/>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-      <c r="B43" s="9"/>
-      <c r="C43" s="9"/>
-      <c r="D43" s="10"/>
-      <c r="E43" s="8"/>
-      <c r="F43" s="8"/>
-      <c r="G43" s="9"/>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-      <c r="B44" s="9"/>
-      <c r="C44" s="9"/>
-      <c r="D44" s="10"/>
-      <c r="E44" s="8"/>
-      <c r="F44" s="8"/>
-      <c r="G44" s="9"/>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-      <c r="B45" s="9"/>
-      <c r="C45" s="9"/>
-      <c r="D45" s="10"/>
-      <c r="E45" s="8"/>
-      <c r="F45" s="8"/>
-      <c r="G45" s="9"/>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-      <c r="B46" s="9"/>
-      <c r="C46" s="9"/>
-      <c r="D46" s="10"/>
-      <c r="E46" s="8"/>
-      <c r="F46" s="8"/>
-      <c r="G46" s="9"/>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-      <c r="B47" s="9"/>
-      <c r="C47" s="9"/>
-      <c r="D47" s="10"/>
-      <c r="E47" s="8"/>
-      <c r="F47" s="8"/>
-      <c r="G47" s="9"/>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-      <c r="B48" s="9"/>
-      <c r="C48" s="9"/>
-      <c r="D48" s="10"/>
-      <c r="E48" s="8"/>
-      <c r="F48" s="8"/>
-      <c r="G48" s="9"/>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
-      <c r="B49" s="9"/>
-      <c r="C49" s="9"/>
-      <c r="D49" s="10"/>
-      <c r="E49" s="8"/>
-      <c r="F49" s="8"/>
-      <c r="G49" s="9"/>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A50" s="8"/>
-      <c r="B50" s="9"/>
-      <c r="C50" s="9"/>
-      <c r="D50" s="10"/>
-      <c r="E50" s="8"/>
-      <c r="F50" s="8"/>
-      <c r="G50" s="9"/>
-    </row>
-  </sheetData>
-  <sheetProtection selectLockedCells="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB9FB10F-C378-4F04-8996-33C7485F9647}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3B33AFB1-6DBB-47C4-AB23-F00FB81CCC17}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{DF24AFE2-1CF8-4DC0-B6EA-A5E1AFAD6B95}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-      </x14:dataValidations>
-    </ext>
-  </extLst>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{96BD9B9A-218D-41F0-B45A-B32BC745B978}">
   <sheetPr>
     <tabColor theme="1"/>
   </sheetPr>
   <dimension ref="A1:C10"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>38</v>
       </c>
@@ -3662,7 +5105,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3673,7 +5116,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -3684,7 +5127,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
@@ -3692,7 +5135,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>39</v>
       </c>
@@ -3700,7 +5143,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>27</v>
       </c>
@@ -3708,7 +5151,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
         <v>28</v>
       </c>
@@ -3716,17 +5159,20 @@
         <v>33</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B8" s="3" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>31</v>
       </c>
@@ -3739,20 +5185,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{11FAA59B-63F0-4F8F-943D-F5C3F5AA7B27}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0AA9C2FE-8638-417A-81F6-F8A47AF399D2}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -3775,7 +5221,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -3797,8 +5243,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -3821,7 +5268,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -3844,7 +5291,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -3867,7 +5314,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -3890,7 +5337,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -3913,7 +5360,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -3936,7 +5383,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -3959,7 +5406,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -3982,7 +5429,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -4005,7 +5452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -4028,7 +5475,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -4051,7 +5498,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -4060,7 +5507,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -4069,7 +5516,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -4078,7 +5525,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -4087,7 +5534,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -4096,7 +5543,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -4105,7 +5552,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -4114,7 +5561,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -4123,7 +5570,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -4132,7 +5579,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -4141,7 +5588,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -4150,7 +5597,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4159,25 +5606,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4186,7 +5633,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -4195,7 +5642,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -4204,7 +5651,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -4213,7 +5660,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -4222,7 +5669,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -4231,7 +5678,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -4240,7 +5687,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -4249,7 +5696,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -4258,7 +5705,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -4267,7 +5714,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -4276,7 +5723,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -4285,7 +5732,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -4294,7 +5741,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -4303,7 +5750,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -4312,7 +5759,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -4321,7 +5768,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -4330,7 +5777,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -4339,7 +5786,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -4348,7 +5795,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -4357,7 +5804,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -4366,7 +5813,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -4375,7 +5822,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -4387,26 +5834,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A1ED27FB-510F-4AAF-BF5D-A93EAE696B7E}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C81F08A0-1437-46E6-8210-8C5E3FB4C3ED}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{69E89BDC-872D-4BBD-8CC0-9DCD08FCFCA2}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A5278FEB-5CCD-40C5-8D4E-3CD1B444BB89}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{856FA88A-1B82-4817-A3DC-18743ECF0217}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{50953B7A-6FB6-49A4-BECA-87682EF1159D}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9660B4EE-36ED-450A-8A4A-B57D6DD8E114}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -4415,20 +5869,20 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7155F253-6C4F-4B7F-98AF-3AE8C061976F}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D8BF98C6-DE3C-49BF-9AB9-458AA8EFCABD}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -4451,7 +5905,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -4473,8 +5927,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -4497,7 +5952,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -4520,7 +5975,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -4543,7 +5998,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -4566,7 +6021,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -4589,7 +6044,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -4612,7 +6067,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -4635,7 +6090,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -4658,7 +6113,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -4681,7 +6136,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -4704,7 +6159,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -4727,7 +6182,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -4736,7 +6191,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -4745,7 +6200,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -4754,7 +6209,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -4763,7 +6218,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -4772,7 +6227,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -4781,7 +6236,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -4790,7 +6245,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -4799,7 +6254,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -4808,7 +6263,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -4817,7 +6272,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -4826,7 +6281,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -4835,25 +6290,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -4862,7 +6317,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -4871,7 +6326,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -4880,7 +6335,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -4889,7 +6344,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -4898,7 +6353,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -4907,7 +6362,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -4916,7 +6371,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -4925,7 +6380,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -4934,7 +6389,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -4943,7 +6398,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -4952,7 +6407,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -4961,7 +6416,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -4970,7 +6425,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -4979,7 +6434,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -4988,7 +6443,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -4997,7 +6452,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -5006,7 +6461,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -5015,7 +6470,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -5024,7 +6479,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -5033,7 +6488,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -5042,7 +6497,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -5051,7 +6506,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -5063,26 +6518,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2C421DB2-69D3-4866-BE92-F9EB4863BE88}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4F7F97F3-25B7-446B-AC9B-938DBD9F4CD0}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9F8E8D7D-E87B-40C0-8B88-938EADC41DF6}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3E228457-702A-4BD0-948A-A00EFCD954A4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{5B2585EE-C7A5-4C70-8655-F20997736E5D}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{6803F1BF-B8D2-412A-84A3-8029CAEE9B24}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D3B178B0-A6C4-4470-BC72-2994AAB358CB}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5091,20 +6553,20 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1C550FF-5AFC-4F3A-8227-67E0968CCCB1}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{568FA4DE-43FC-4021-8C25-74D3B95E502D}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -5127,7 +6589,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5149,8 +6611,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5173,7 +6636,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5196,7 +6659,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5219,7 +6682,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5242,7 +6705,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5265,7 +6728,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5288,7 +6751,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5311,7 +6774,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -5334,7 +6797,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -5357,7 +6820,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -5380,7 +6843,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -5403,7 +6866,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -5412,7 +6875,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -5421,7 +6884,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -5430,7 +6893,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -5439,7 +6902,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -5448,7 +6911,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -5457,7 +6920,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -5466,7 +6929,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -5475,7 +6938,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -5484,7 +6947,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -5493,7 +6956,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -5502,7 +6965,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -5511,25 +6974,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -5538,7 +7001,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -5547,7 +7010,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -5556,7 +7019,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -5565,7 +7028,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -5574,7 +7037,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -5583,7 +7046,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -5592,7 +7055,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -5601,7 +7064,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -5610,7 +7073,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -5619,7 +7082,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -5628,7 +7091,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -5637,7 +7100,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -5646,7 +7109,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -5655,7 +7118,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -5664,7 +7127,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -5673,7 +7136,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -5682,7 +7145,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -5691,7 +7154,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -5700,7 +7163,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -5709,7 +7172,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -5718,7 +7181,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -5727,7 +7190,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -5739,26 +7202,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{53B67F3F-F84F-4A03-80A3-78FD17D1D335}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{244A83D1-CAFF-4B59-B28A-9B413C6DCBEB}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0CAFC14C-7A5E-48DA-909A-10FFE760C34F}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1E578B4E-4FE4-4EBA-BA17-73962425563D}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{89A4B238-1574-44EC-92D8-8ED3DB9EC0F1}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{30B33974-B010-4DB2-ADE1-A6B2DC105480}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{2ACC0661-FC43-4488-A2CC-6CEFB34802A5}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5767,20 +7237,20 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{833D4882-C656-4B31-8C85-99FE25188C51}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C73D43D7-86D0-469A-883A-0D6F54FB2C43}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -5803,7 +7273,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -5825,8 +7295,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -5849,7 +7320,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -5872,7 +7343,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -5895,7 +7366,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -5918,7 +7389,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -5941,7 +7412,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -5964,7 +7435,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -5987,7 +7458,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -6010,7 +7481,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -6033,7 +7504,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -6056,7 +7527,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -6079,7 +7550,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -6088,7 +7559,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -6097,7 +7568,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -6106,7 +7577,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6115,7 +7586,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -6124,7 +7595,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6133,7 +7604,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -6142,7 +7613,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -6151,7 +7622,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -6160,7 +7631,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -6169,7 +7640,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -6178,7 +7649,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -6187,25 +7658,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -6214,7 +7685,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -6223,7 +7694,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -6232,7 +7703,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -6241,7 +7712,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -6250,7 +7721,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -6259,7 +7730,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -6268,7 +7739,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -6277,7 +7748,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -6286,7 +7757,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -6295,7 +7766,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -6304,7 +7775,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -6313,7 +7784,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -6322,7 +7793,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -6331,7 +7802,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -6340,7 +7811,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -6349,7 +7820,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -6358,7 +7829,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -6367,7 +7838,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -6376,7 +7847,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -6385,7 +7856,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -6394,7 +7865,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -6403,7 +7874,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -6415,26 +7886,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{439A3C50-6671-4FA7-AB0A-7F03C83DF875}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AE1D0ACC-4596-432C-A779-A5D9412BC879}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{89D99B96-B8DD-4C85-83C2-198A35473793}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C1A1EE16-E1DF-40FD-9E2C-6E7C4A434001}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CECEE561-503F-4FAD-AA23-CA5E3ED430EC}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{99E61024-3202-4795-B5AD-735EEA126909}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BDE9E204-44FA-4043-8854-186835EFE9B4}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -6443,20 +7921,20 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F3E4DBD-1655-4355-9CD8-4371C3619257}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F00C840-F105-435A-9BAB-F3ADD6D73928}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -6479,7 +7957,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -6501,8 +7979,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -6525,7 +8004,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -6548,7 +8027,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -6571,7 +8050,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -6594,7 +8073,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -6617,7 +8096,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -6640,7 +8119,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -6663,7 +8142,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -6686,7 +8165,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -6709,7 +8188,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -6732,7 +8211,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -6755,7 +8234,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -6764,7 +8243,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -6773,7 +8252,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -6782,7 +8261,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -6791,7 +8270,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -6800,7 +8279,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -6809,7 +8288,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -6818,7 +8297,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -6827,7 +8306,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -6836,7 +8315,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -6845,7 +8324,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -6854,7 +8333,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -6863,25 +8342,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -6890,7 +8369,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -6899,7 +8378,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -6908,7 +8387,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -6917,7 +8396,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -6926,7 +8405,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -6935,7 +8414,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -6944,7 +8423,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -6953,7 +8432,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -6962,7 +8441,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -6971,7 +8450,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -6980,7 +8459,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -6989,7 +8468,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -6998,7 +8477,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -7007,7 +8486,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -7016,7 +8495,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -7025,7 +8504,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -7034,7 +8513,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -7043,7 +8522,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -7052,7 +8531,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -7061,7 +8540,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -7070,7 +8549,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -7079,7 +8558,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -7091,26 +8570,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{08FD9D23-953D-43A7-9517-64CB6D39F292}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1ABA84C6-8DBE-414E-AAF9-742BA7D9134E}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{4135FCE5-3621-4C42-B5BF-61846703BB7C}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EA8DABF6-C801-4022-AFB3-7EB943205CE2}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{E74F6D99-A629-4587-B116-A8B9F8BDAEAA}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BB990AC9-D359-465A-9B71-D1FF2E71231F}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{284D1C48-0F5C-47A0-9F9D-6656840EA7FD}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7119,20 +8605,20 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18053B99-AE72-4C1D-AA08-FD60AC759E64}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B16B846-6CCD-43E2-AF28-339324B0BCAB}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -7155,7 +8641,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -7177,8 +8663,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -7201,7 +8688,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -7224,7 +8711,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -7247,7 +8734,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -7270,7 +8757,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -7293,7 +8780,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -7316,7 +8803,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -7339,7 +8826,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -7362,7 +8849,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -7385,7 +8872,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -7408,7 +8895,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -7431,7 +8918,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -7440,7 +8927,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -7449,7 +8936,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -7458,7 +8945,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -7467,7 +8954,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -7476,7 +8963,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -7485,7 +8972,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -7494,7 +8981,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -7503,7 +8990,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -7512,7 +8999,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -7521,7 +9008,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -7530,7 +9017,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -7539,25 +9026,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -7566,7 +9053,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -7575,7 +9062,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -7584,7 +9071,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -7593,7 +9080,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -7602,7 +9089,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -7611,7 +9098,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -7620,7 +9107,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -7629,7 +9116,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -7638,7 +9125,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -7647,7 +9134,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -7656,7 +9143,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -7665,7 +9152,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -7674,7 +9161,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -7683,7 +9170,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -7692,7 +9179,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -7701,7 +9188,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -7710,7 +9197,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -7719,7 +9206,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -7728,7 +9215,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -7737,7 +9224,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -7746,7 +9233,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -7755,7 +9242,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -7767,26 +9254,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{544FEF69-17F8-44E4-8F39-E4F9F2CAC18C}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{49F18CD7-7926-490E-AB01-05C8BC5A6120}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{79F64112-B12E-42A9-871C-AB2180CE92C4}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{1ACA399A-D44A-4880-B6D6-504B59B78250}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7190D654-8A52-4FF6-9ADA-DB1A03351853}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B1A4FD8D-6C8B-47E1-8F6F-A2ABE266141E}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{CAD13994-E78E-4483-B358-EAD4DEC56BEA}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7795,20 +9289,20 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CE4077A-9BE0-4A0F-9281-3B42F8A4F179}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4720709-F100-4C84-8292-4E44A1BC1533}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -7831,7 +9325,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -7853,8 +9347,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -7877,7 +9372,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -7900,7 +9395,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -7923,7 +9418,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -7946,7 +9441,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -7969,7 +9464,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -7992,7 +9487,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -8015,7 +9510,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -8038,7 +9533,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -8061,7 +9556,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -8084,7 +9579,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -8107,7 +9602,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -8116,7 +9611,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -8125,7 +9620,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -8134,7 +9629,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -8143,7 +9638,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -8152,7 +9647,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -8161,7 +9656,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -8170,7 +9665,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -8179,7 +9674,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8188,7 +9683,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -8197,7 +9692,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -8206,7 +9701,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -8215,25 +9710,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -8242,7 +9737,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -8251,7 +9746,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -8260,7 +9755,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -8269,7 +9764,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -8278,7 +9773,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -8287,7 +9782,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -8296,7 +9791,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -8305,7 +9800,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -8314,7 +9809,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -8323,7 +9818,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -8332,7 +9827,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -8341,7 +9836,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -8350,7 +9845,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -8359,7 +9854,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -8368,7 +9863,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -8377,7 +9872,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -8386,7 +9881,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -8395,7 +9890,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -8404,7 +9899,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -8413,7 +9908,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -8422,7 +9917,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -8431,7 +9926,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -8443,26 +9938,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{AFBAED14-C80F-4A2C-ACD1-ABC2247E30CC}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EB67EC8-6AAD-4B77-A31A-669784C519C6}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{EE17C8CD-A80F-4FB3-9026-9825E5DCB3B9}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7EF0615D-9F73-4465-A6F2-5B5B7C4B733C}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9D6E18A9-072D-4C47-AD4A-6E1D791C43D8}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{8BBD49E8-846F-4B24-B444-E338ACD655D1}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{05C34CC6-1249-46E7-9DCE-AF078C862C81}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -8471,20 +9973,20 @@
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE64B04-0035-4AE3-A6F2-42D691EA0702}">
-  <dimension ref="A1:G50"/>
-  <sheetFormatPr defaultRowHeight="12.5" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7A0C1046-1278-4979-939A-4D7973E56ADD}">
+  <dimension ref="A1:I50"/>
+  <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="16.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.26953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="31.7265625" style="15" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.453125" style="14" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.1796875" style="14" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.81640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" style="14" customWidth="1"/>
+    <col min="2" max="2" width="15.140625" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" customWidth="1"/>
+    <col min="4" max="4" width="18.42578125" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="14" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.140625" style="14" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="11" t="s">
         <v>46</v>
       </c>
@@ -8507,7 +10009,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="4">
         <v>1</v>
       </c>
@@ -8529,8 +10031,9 @@
       <c r="G2" s="5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="I2" s="3"/>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="4">
         <v>2</v>
       </c>
@@ -8553,7 +10056,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="4">
         <v>3</v>
       </c>
@@ -8576,7 +10079,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="4">
         <v>4</v>
       </c>
@@ -8599,7 +10102,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="4">
         <v>5</v>
       </c>
@@ -8622,7 +10125,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="4">
         <v>6</v>
       </c>
@@ -8645,7 +10148,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="4">
         <v>7</v>
       </c>
@@ -8668,7 +10171,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="4">
         <v>8</v>
       </c>
@@ -8691,7 +10194,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="4">
         <v>9</v>
       </c>
@@ -8714,7 +10217,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="4">
         <v>10</v>
       </c>
@@ -8737,7 +10240,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="4">
         <v>11</v>
       </c>
@@ -8760,7 +10263,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="4">
         <v>12</v>
       </c>
@@ -8783,7 +10286,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="8"/>
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
@@ -8792,7 +10295,7 @@
       <c r="F14" s="8"/>
       <c r="G14" s="9"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="8"/>
       <c r="B15" s="9"/>
       <c r="C15" s="9"/>
@@ -8801,7 +10304,7 @@
       <c r="F15" s="8"/>
       <c r="G15" s="9"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="8"/>
       <c r="B16" s="9"/>
       <c r="C16" s="9"/>
@@ -8810,7 +10313,7 @@
       <c r="F16" s="8"/>
       <c r="G16" s="9"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A17" s="8"/>
       <c r="B17" s="9"/>
       <c r="C17" s="9"/>
@@ -8819,7 +10322,7 @@
       <c r="F17" s="8"/>
       <c r="G17" s="9"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A18" s="8"/>
       <c r="B18" s="9"/>
       <c r="C18" s="9"/>
@@ -8828,7 +10331,7 @@
       <c r="F18" s="8"/>
       <c r="G18" s="9"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A19" s="8"/>
       <c r="B19" s="9"/>
       <c r="C19" s="9"/>
@@ -8837,7 +10340,7 @@
       <c r="F19" s="8"/>
       <c r="G19" s="9"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A20" s="8"/>
       <c r="B20" s="9"/>
       <c r="C20" s="9"/>
@@ -8846,7 +10349,7 @@
       <c r="F20" s="8"/>
       <c r="G20" s="9"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A21" s="8"/>
       <c r="B21" s="9"/>
       <c r="C21" s="9"/>
@@ -8855,7 +10358,7 @@
       <c r="F21" s="8"/>
       <c r="G21" s="9"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A22" s="8"/>
       <c r="B22" s="9"/>
       <c r="C22" s="9"/>
@@ -8864,7 +10367,7 @@
       <c r="F22" s="8"/>
       <c r="G22" s="9"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A23" s="8"/>
       <c r="B23" s="9"/>
       <c r="C23" s="9"/>
@@ -8873,7 +10376,7 @@
       <c r="F23" s="8"/>
       <c r="G23" s="9"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A24" s="8"/>
       <c r="B24" s="9"/>
       <c r="C24" s="9"/>
@@ -8882,7 +10385,7 @@
       <c r="F24" s="8"/>
       <c r="G24" s="9"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A25" s="8"/>
       <c r="B25" s="9"/>
       <c r="C25" s="9"/>
@@ -8891,25 +10394,25 @@
       <c r="F25" s="8"/>
       <c r="G25" s="9"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A26" s="8"/>
       <c r="B26" s="9"/>
-      <c r="C26" s="9"/>
-      <c r="D26" s="10"/>
+      <c r="C26" s="10"/>
+      <c r="D26" s="8"/>
       <c r="E26" s="8"/>
       <c r="F26" s="8"/>
       <c r="G26" s="9"/>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A27" s="8"/>
       <c r="B27" s="9"/>
-      <c r="C27" s="9"/>
-      <c r="D27" s="10"/>
+      <c r="C27" s="10"/>
+      <c r="D27" s="8"/>
       <c r="E27" s="8"/>
       <c r="F27" s="8"/>
       <c r="G27" s="9"/>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A28" s="8"/>
       <c r="B28" s="9"/>
       <c r="C28" s="9"/>
@@ -8918,7 +10421,7 @@
       <c r="F28" s="8"/>
       <c r="G28" s="9"/>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A29" s="8"/>
       <c r="B29" s="9"/>
       <c r="C29" s="9"/>
@@ -8927,7 +10430,7 @@
       <c r="F29" s="8"/>
       <c r="G29" s="9"/>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A30" s="8"/>
       <c r="B30" s="9"/>
       <c r="C30" s="9"/>
@@ -8936,7 +10439,7 @@
       <c r="F30" s="8"/>
       <c r="G30" s="9"/>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A31" s="8"/>
       <c r="B31" s="9"/>
       <c r="C31" s="9"/>
@@ -8945,7 +10448,7 @@
       <c r="F31" s="8"/>
       <c r="G31" s="9"/>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A32" s="8"/>
       <c r="B32" s="9"/>
       <c r="C32" s="9"/>
@@ -8954,7 +10457,7 @@
       <c r="F32" s="8"/>
       <c r="G32" s="9"/>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A33" s="8"/>
       <c r="B33" s="9"/>
       <c r="C33" s="9"/>
@@ -8963,7 +10466,7 @@
       <c r="F33" s="8"/>
       <c r="G33" s="9"/>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A34" s="8"/>
       <c r="B34" s="9"/>
       <c r="C34" s="9"/>
@@ -8972,7 +10475,7 @@
       <c r="F34" s="8"/>
       <c r="G34" s="9"/>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A35" s="8"/>
       <c r="B35" s="9"/>
       <c r="C35" s="9"/>
@@ -8981,7 +10484,7 @@
       <c r="F35" s="8"/>
       <c r="G35" s="9"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A36" s="8"/>
       <c r="B36" s="9"/>
       <c r="C36" s="9"/>
@@ -8990,7 +10493,7 @@
       <c r="F36" s="8"/>
       <c r="G36" s="9"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A37" s="8"/>
       <c r="B37" s="9"/>
       <c r="C37" s="9"/>
@@ -8999,7 +10502,7 @@
       <c r="F37" s="8"/>
       <c r="G37" s="9"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A38" s="8"/>
       <c r="B38" s="9"/>
       <c r="C38" s="9"/>
@@ -9008,7 +10511,7 @@
       <c r="F38" s="8"/>
       <c r="G38" s="9"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A39" s="8"/>
       <c r="B39" s="9"/>
       <c r="C39" s="9"/>
@@ -9017,7 +10520,7 @@
       <c r="F39" s="8"/>
       <c r="G39" s="9"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A40" s="8"/>
       <c r="B40" s="9"/>
       <c r="C40" s="9"/>
@@ -9026,7 +10529,7 @@
       <c r="F40" s="8"/>
       <c r="G40" s="9"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A41" s="8"/>
       <c r="B41" s="9"/>
       <c r="C41" s="9"/>
@@ -9035,7 +10538,7 @@
       <c r="F41" s="8"/>
       <c r="G41" s="9"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A42" s="8"/>
       <c r="B42" s="9"/>
       <c r="C42" s="9"/>
@@ -9044,7 +10547,7 @@
       <c r="F42" s="8"/>
       <c r="G42" s="9"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A43" s="8"/>
       <c r="B43" s="9"/>
       <c r="C43" s="9"/>
@@ -9053,7 +10556,7 @@
       <c r="F43" s="8"/>
       <c r="G43" s="9"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A44" s="8"/>
       <c r="B44" s="9"/>
       <c r="C44" s="9"/>
@@ -9062,7 +10565,7 @@
       <c r="F44" s="8"/>
       <c r="G44" s="9"/>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A45" s="8"/>
       <c r="B45" s="9"/>
       <c r="C45" s="9"/>
@@ -9071,7 +10574,7 @@
       <c r="F45" s="8"/>
       <c r="G45" s="9"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A46" s="8"/>
       <c r="B46" s="9"/>
       <c r="C46" s="9"/>
@@ -9080,7 +10583,7 @@
       <c r="F46" s="8"/>
       <c r="G46" s="9"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A47" s="8"/>
       <c r="B47" s="9"/>
       <c r="C47" s="9"/>
@@ -9089,7 +10592,7 @@
       <c r="F47" s="8"/>
       <c r="G47" s="9"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A48" s="8"/>
       <c r="B48" s="9"/>
       <c r="C48" s="9"/>
@@ -9098,7 +10601,7 @@
       <c r="F48" s="8"/>
       <c r="G48" s="9"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A49" s="8"/>
       <c r="B49" s="9"/>
       <c r="C49" s="9"/>
@@ -9107,7 +10610,7 @@
       <c r="F49" s="8"/>
       <c r="G49" s="9"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A50" s="8"/>
       <c r="B50" s="9"/>
       <c r="C50" s="9"/>
@@ -9119,26 +10622,33 @@
   </sheetData>
   <sheetProtection selectLockedCells="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{9FEAA97F-8F0C-4449-BE6A-389E2A3B3074}">
-          <x14:formula1>
-            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
-          </x14:formula1>
-          <xm:sqref>E2:E1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{0DB0462F-5659-42FE-8277-0120A34CA962}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="4">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{F7EA8898-DFCE-440B-AA60-12DE64EDA929}">
           <x14:formula1>
             <xm:f>Dropdownlist!$B$2:$B$7</xm:f>
           </x14:formula1>
-          <xm:sqref>G2:G1048576</xm:sqref>
+          <xm:sqref>G51:G1048576</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BA6BB860-2142-40ED-8006-E0F5088245C4}">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{84F8F477-267D-44C0-8D8E-4F48736CB9F5}">
           <x14:formula1>
             <xm:f>Dropdownlist!$A$2:$A$10</xm:f>
           </x14:formula1>
           <xm:sqref>F2:F1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{D52EC615-090B-4394-95A2-988F6C2170ED}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$C$2:$C$3</xm:f>
+          </x14:formula1>
+          <xm:sqref>E2:E26 E29:E1048576 D26:D27</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{BE1175B8-9076-42D6-8BF0-061466E8B069}">
+          <x14:formula1>
+            <xm:f>Dropdownlist!$B$2:$B$8</xm:f>
+          </x14:formula1>
+          <xm:sqref>G2:G50</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/CPMT_template.xlsx
+++ b/CPMT_template.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seche\Documents\Benoit\Handball\TeamPointMonitoringTool\CTPM\static\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\seche\Documents\Benoit\Handball\TeamPointMonitoringTool\CPMT-web\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CD715D4D-EE9F-42BD-8886-A2F91B9B952E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Team (1)" sheetId="51" r:id="rId1"/>
